--- a/data/trans_dic/IP44C$otros_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido algún retraso en otros pagos</t>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,24</t>
+          <t>0,77; 6,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,12</t>
+          <t>1,01; 8,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,11</t>
+          <t>1,33; 6,11</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,99</t>
+          <t>1,21; 9,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,22</t>
+          <t>0,72; 6,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,63</t>
+          <t>1,48; 5,63</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 16,66</t>
+          <t>3,04; 16,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,31</t>
+          <t>0,0; 6,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 9,37</t>
+          <t>2,28; 9,68</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 48,68</t>
+          <t>2,66; 47,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,13</t>
+          <t>2,24; 7,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 28,61</t>
+          <t>3,24; 29,05</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 20,81</t>
+          <t>4,75; 19,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,89</t>
+          <t>2,27; 8,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 12,45</t>
+          <t>4,15; 11,26</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 14,47</t>
+          <t>2,62; 13,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,79; 19,48</t>
+          <t>4,84; 18,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 13,04</t>
+          <t>4,8; 13,41</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 21,09</t>
+          <t>4,66; 24,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,73</t>
+          <t>3,02; 5,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 12,54</t>
+          <t>4,32; 14,71</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4693</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7190</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>787; 6385</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1352; 11864</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3155; 14455</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3541</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2241</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5782</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1148; 8536</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>686; 5781</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2809; 10710</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5716</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1575; 8770</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4189</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2644; 11202</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>32929</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8886</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>41815</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5695; 102171</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4765; 15111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13826; 124007</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11005</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7147</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18152</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5439; 22544</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3565; 12680</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11263; 30553</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6873</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11588</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1742; 9162</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3332; 12627</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6499; 18148</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>59082</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>31161</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>90243</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>30026; 156412</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>22111; 41982</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>59393; 202487</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$otros_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,21</t>
+          <t>0,73; 6,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 8,86</t>
+          <t>0,94; 8,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,11</t>
+          <t>1,36; 6,17</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,02</t>
+          <t>1,22; 8,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,05</t>
+          <t>0,39; 6,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,63</t>
+          <t>1,48; 5,58</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 16,91</t>
+          <t>3,52; 17,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,56</t>
+          <t>0,0; 7,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 9,68</t>
+          <t>2,32; 9,15</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 47,68</t>
+          <t>2,55; 49,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,11</t>
+          <t>2,22; 7,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 29,05</t>
+          <t>3,21; 27,46</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 19,68</t>
+          <t>4,91; 19,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 8,08</t>
+          <t>2,38; 8,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 11,26</t>
+          <t>4,11; 10,9</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 13,79</t>
+          <t>2,58; 14,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 18,33</t>
+          <t>4,71; 18,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 13,41</t>
+          <t>4,78; 13,2</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 24,26</t>
+          <t>4,49; 22,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,74</t>
+          <t>3,09; 5,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 14,71</t>
+          <t>4,37; 13,2</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>787; 6385</t>
+          <t>752; 6738</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1352; 11864</t>
+          <t>1257; 12026</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3155; 14455</t>
+          <t>3212; 14594</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1148; 8536</t>
+          <t>1158; 8054</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>686; 5781</t>
+          <t>368; 5830</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2809; 10710</t>
+          <t>2813; 10615</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1575; 8770</t>
+          <t>1825; 9174</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4189</t>
+          <t>0; 4981</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2644; 11202</t>
+          <t>2680; 10587</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5695; 102171</t>
+          <t>5469; 106162</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4765; 15111</t>
+          <t>4712; 15111</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13826; 124007</t>
+          <t>13710; 117233</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5439; 22544</t>
+          <t>5627; 21939</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3565; 12680</t>
+          <t>3733; 13309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11263; 30553</t>
+          <t>11162; 29584</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1742; 9162</t>
+          <t>1715; 9402</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3332; 12627</t>
+          <t>3248; 12929</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6499; 18148</t>
+          <t>6472; 17867</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30026; 156412</t>
+          <t>28965; 144985</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22111; 41982</t>
+          <t>22598; 42017</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59393; 202487</t>
+          <t>60140; 181709</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$otros_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,55</t>
+          <t>0,87; 9,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,98</t>
+          <t>0,68; 6,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,17</t>
+          <t>1,42; 6,52</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 8,51</t>
+          <t>0,5; 6,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,1</t>
+          <t>1,24; 8,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,58</t>
+          <t>1,39; 5,81</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 17,69</t>
+          <t>0,0; 7,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,8</t>
+          <t>3,54; 17,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,15</t>
+          <t>2,38; 10,09</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 49,55</t>
+          <t>2,29; 7,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,11</t>
+          <t>2,44; 10,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 27,46</t>
+          <t>2,93; 8,04</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 19,16</t>
+          <t>2,39; 8,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,48</t>
+          <t>3,98; 12,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,9</t>
+          <t>3,82; 9,35</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,58; 14,15</t>
+          <t>4,61; 19,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 18,77</t>
+          <t>2,71; 15,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 13,2</t>
+          <t>5,11; 13,85</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 22,49</t>
+          <t>3,22; 6,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,74</t>
+          <t>3,92; 7,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 13,2</t>
+          <t>3,96; 6,25</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>6692</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>752; 6738</t>
+          <t>1045; 11558</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1257; 12026</t>
+          <t>689; 6639</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3212; 14594</t>
+          <t>3141; 14397</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5837</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1158; 8054</t>
+          <t>460; 6006</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>368; 5830</t>
+          <t>1201; 8075</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2813; 10615</t>
+          <t>2614; 10916</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5862</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1825; 9174</t>
+          <t>0; 4062</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4981</t>
+          <t>1895; 9521</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2680; 10587</t>
+          <t>2626; 11141</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>32929</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41815</t>
+          <t>17289</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5469; 106162</t>
+          <t>4493; 14914</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4712; 15111</t>
+          <t>4291; 18310</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13710; 117233</t>
+          <t>10923; 29942</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>15491</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5627; 21939</t>
+          <t>3393; 12615</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3733; 13309</t>
+          <t>4541; 14080</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11162; 29584</t>
+          <t>9787; 23917</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11701</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1715; 9402</t>
+          <t>3020; 12850</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3248; 12929</t>
+          <t>1844; 10241</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6472; 17867</t>
+          <t>6828; 18488</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>59082</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90243</t>
+          <t>62871</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>28965; 144985</t>
+          <t>21605; 40698</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22598; 42017</t>
+          <t>23866; 44723</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60140; 181709</t>
+          <t>50785; 80071</t>
         </is>
       </c>
     </row>
